--- a/docs/examples/analytics/05_Plan_Goal_Pencapaian_KPI.xlsx
+++ b/docs/examples/analytics/05_Plan_Goal_Pencapaian_KPI.xlsx
@@ -10,28 +10,32 @@
     <sheet name="BACA_DULU" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Kamus_Data" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rencana_ETL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Master_Unit" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Master_Tim" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Master_Indikator" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="KPI_Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="KPI_Measurement" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="KPI_Result" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Action_Plan" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Formula_Analitik" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Aturan_Action_Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Master_Unit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Master_Tim" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Master_Indikator" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="KPI_Plan" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="KPI_Measurement" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="KPI_Result" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Action_Plan" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="REF_unit_code">'Master_Unit'!$A$2:$A$4</definedName>
     <definedName name="REF_owner_team_code">'Master_Tim'!$A$2:$A$4</definedName>
     <definedName name="REF_indicator_code">'Master_Indikator'!$A$2:$A$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BACA_DULU'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BACA_DULU'!$A$1:$B$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kamus_Data'!$A$1:$G$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rencana_ETL'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Master_Unit'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Master_Tim'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Master_Indikator'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'KPI_Plan'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'KPI_Measurement'!$A$1:$J$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'KPI_Result'!$A$1:$S$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Action_Plan'!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rencana_ETL'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Formula_Analitik'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Aturan_Action_Plan'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Master_Unit'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Master_Tim'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Master_Indikator'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'KPI_Plan'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'KPI_Measurement'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'KPI_Result'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Action_Plan'!$A$1:$W$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -600,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -711,7 +715,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Master_* = MASTER. Tab data/rekap/Action_Plan = NON_MASTER. BACA_DULU, Kamus_Data, Rencana_ETL = petunjuk, Dikecualikan dari ETL.</t>
+          <t>Master_* = MASTER. Tab data/rekap/Action_Plan = NON_MASTER. BACA_DULU, Kamus_Data, Rencana_ETL, Formula_Analitik, Aturan_Action_Plan = Dikecualikan dari ETL. Dua tab kontrol diimpor melalui API analytics-rules.</t>
         </is>
       </c>
     </row>
@@ -739,13 +743,2225 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Formula dan aturan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Angka persentase memakai 0..1: 50% = 0.50. Formula memakai kode metrik aplikasi, tanpa =Excel, SQL, script atau fungsi bebas. Formula dependency harus diletakkan setelah formula acuannya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Impor aturan API</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/v1/analytics-rules/import-sheet memakai source_id, name, product_code dan query. Lihat rules/*.json dalam ZIP atau docs/PANDUAN_ATURAN_ANALITIK.md. Preview, reviewer berbeda menyetujui expected_hash, lalu evaluate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Produk aturan</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>demo_kpi_kpi_result</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Query aturan (JSON)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>{"join_relationships": [], "metrics": ["m_revenue_actual_value", "m_revenue_target_value"], "dimensions": ["plan_id", "unit_code", "indicator_code"], "filters": [{"field": "period_start", "operator": "between", "value": ["2026-01-01", "2026-01-31"]}, {"field": "indicator_code", "operator": "eq", "value": "REVENUE"}], "sort": [], "time_grain": "none", "limit": 1000, "offset": 0, "visualization": null}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002563EB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>measurement_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>unit_code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>indicator_code</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>measured_at</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>measured_value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>measurement_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_ref</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>method_version</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>collected_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-0-0</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-REVENUE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-MKT</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-0-0</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-0-1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-REVENUE</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-MKT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-0-1</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-REVENUE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-MKT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>900000</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-0-2</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-1-0</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-RESOLVED</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-1-0</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-1-1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-RESOLVED</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-1-1</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-1-2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-RESOLVED</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-1-2</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-2-0</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-2-0</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-2-1</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-2-1</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-2-2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-2-2</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-3-0</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-SATISFACTION</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-3-0</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-3-1</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-SATISFACTION</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-3-1</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-1-3-2</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-1-SATISFACTION</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-1-3-2</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-0-0</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-REVENUE</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-MKT</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>770000</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-0-0</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-0-1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-REVENUE</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-MKT</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>880000</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-0-1</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-0-2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-REVENUE</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-MKT</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>990000</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-0-2</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-1-0</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-RESOLVED</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-1-0</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-1-1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-RESOLVED</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-1-1</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-1-2</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-RESOLVED</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-1-2</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-2-0</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-2-0</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-2-1</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-2-1</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-2-2</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSE_HOURS</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>HOUR</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-2-2</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-3-0</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-SATISFACTION</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-3-0</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-3-1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-SATISFACTION</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-3-1</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MEAS-2-3-2</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>PLAN-2-SATISFACTION</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>UNIT-CS</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>SATISFACTION</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14T09:00:00+07:00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>SCORE_1_5</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>SIMULASI-MEAS-2-3-2</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>METHOD-V1</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-03T09:00:00+07:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J25"/>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <formula1>=REF_unit_code</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <formula1>=REF_indicator_code</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<s:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:sheetPr>
+    <s:tabColor rgb="002563EB"/>
+    <s:outlinePr summaryBelow="1" summaryRight="1"/>
+    <s:pageSetUpPr/>
+  </s:sheetPr>
+  <s:dimension ref="A1:S9"/>
+  <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <s:cols>
+    <s:col width="18" customWidth="1" min="1" max="1"/>
+    <s:col width="18" customWidth="1" min="2" max="2"/>
+    <s:col width="18" customWidth="1" min="3" max="3"/>
+    <s:col width="18" customWidth="1" min="4" max="4"/>
+    <s:col width="18" customWidth="1" min="5" max="5"/>
+    <s:col width="18" customWidth="1" min="6" max="6"/>
+    <s:col width="18" customWidth="1" min="7" max="7"/>
+    <s:col width="19" customWidth="1" min="8" max="8"/>
+    <s:col width="18" customWidth="1" min="9" max="9"/>
+    <s:col width="18" customWidth="1" min="10" max="10"/>
+    <s:col width="18" customWidth="1" min="11" max="11"/>
+    <s:col width="18" customWidth="1" min="12" max="12"/>
+    <s:col width="18" customWidth="1" min="13" max="13"/>
+    <s:col width="19" customWidth="1" min="14" max="14"/>
+    <s:col width="20" customWidth="1" min="15" max="15"/>
+    <s:col width="18" customWidth="1" min="16" max="16"/>
+    <s:col width="19" customWidth="1" min="17" max="17"/>
+    <s:col width="18" customWidth="1" min="18" max="18"/>
+    <s:col width="18" customWidth="1" min="19" max="19"/>
+  </s:cols>
+  <s:sheetData>
+    <s:row r="1" ht="32" customHeight="1">
+      <s:c r="A1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>kpi_result_id</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>plan_id</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>goal_id</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>unit_code</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>indicator_code</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>period_start</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>period_end</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>measurement_unit</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>direction</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>aggregation</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>target_value</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="L1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>actual_value</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="M1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>sample_count</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="N1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>unfavourable_gap</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="O1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>achievement_ratio</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="P1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>result_status</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="Q1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>reporting_status</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>collected_at</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>data_as_of_at</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="2">
+      <s:c r="A2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-1-REVENUE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-1-REVENUE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-MKT</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>REVENUE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>IDR</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HIGHER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SUM</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K2" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B2)</s:f>
+        <s:v>3000000</s:v>
+      </s:c>
+      <s:c r="L2" s="4">
+        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B2)</s:f>
+        <s:v>2400000</s:v>
+      </s:c>
+      <s:c r="M2" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B2)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N2" s="4">
+        <s:f>IF(I2="HIGHER_IS_BETTER",MAX(0,K2-L2),MAX(0,L2-K2))</s:f>
+        <s:v>600000</s:v>
+      </s:c>
+      <s:c r="O2" s="5">
+        <s:f>IF(I2="HIGHER_IS_BETTER",IF(K2&gt;0,L2/K2,""),IF(L2&gt;0,K2/L2,""))</s:f>
+        <s:v>0.8</s:v>
+      </s:c>
+      <s:c r="P2" s="3" t="str">
+        <s:f>IF(IF(I2="HIGHER_IS_BETTER",L2&gt;=K2,L2&lt;=K2),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S2" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="3">
+      <s:c r="A3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-1-RESOLVED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-1-RESOLVED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-CS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESOLVED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>CASE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HIGHER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SUM</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K3" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B3)</s:f>
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="L3" s="4">
+        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B3)</s:f>
+        <s:v>24</s:v>
+      </s:c>
+      <s:c r="M3" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B3)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N3" s="4">
+        <s:f>IF(I3="HIGHER_IS_BETTER",MAX(0,K3-L3),MAX(0,L3-K3))</s:f>
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="O3" s="5">
+        <s:f>IF(I3="HIGHER_IS_BETTER",IF(K3&gt;0,L3/K3,""),IF(L3&gt;0,K3/L3,""))</s:f>
+        <s:v>0.8</s:v>
+      </s:c>
+      <s:c r="P3" s="3" t="str">
+        <s:f>IF(IF(I3="HIGHER_IS_BETTER",L3&gt;=K3,L3&lt;=K3),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S3" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="4">
+      <s:c r="A4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-1-RESPONSE_HOURS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-1-RESPONSE_HOURS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-CS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESPONSE_HOURS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HOUR</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>LOWER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>AVG</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K4" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B4)</s:f>
+        <s:v>24</s:v>
+      </s:c>
+      <s:c r="L4" s="4">
+        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B4)</s:f>
+        <s:v>30.0</s:v>
+      </s:c>
+      <s:c r="M4" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B4)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N4" s="4">
+        <s:f>IF(I4="HIGHER_IS_BETTER",MAX(0,K4-L4),MAX(0,L4-K4))</s:f>
+        <s:v>6.0</s:v>
+      </s:c>
+      <s:c r="O4" s="5">
+        <s:f>IF(I4="HIGHER_IS_BETTER",IF(K4&gt;0,L4/K4,""),IF(L4&gt;0,K4/L4,""))</s:f>
+        <s:v>0.8</s:v>
+      </s:c>
+      <s:c r="P4" s="3" t="str">
+        <s:f>IF(IF(I4="HIGHER_IS_BETTER",L4&gt;=K4,L4&lt;=K4),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S4" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="5">
+      <s:c r="A5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-1-SATISFACTION</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-1-SATISFACTION</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-CS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SATISFACTION</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-01-31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SCORE_1_5</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HIGHER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>AVG</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K5" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B5)</s:f>
+        <s:v>4.0</s:v>
+      </s:c>
+      <s:c r="L5" s="4">
+        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B5)</s:f>
+        <s:v>3.333333</s:v>
+      </s:c>
+      <s:c r="M5" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B5)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N5" s="4">
+        <s:f>IF(I5="HIGHER_IS_BETTER",MAX(0,K5-L5),MAX(0,L5-K5))</s:f>
+        <s:v>0.666667</s:v>
+      </s:c>
+      <s:c r="O5" s="5">
+        <s:f>IF(I5="HIGHER_IS_BETTER",IF(K5&gt;0,L5/K5,""),IF(L5&gt;0,K5/L5,""))</s:f>
+        <s:v>0.833333</s:v>
+      </s:c>
+      <s:c r="P5" s="3" t="str">
+        <s:f>IF(IF(I5="HIGHER_IS_BETTER",L5&gt;=K5,L5&lt;=K5),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S5" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="6">
+      <s:c r="A6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-2-REVENUE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-2-REVENUE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-MKT</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>REVENUE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>IDR</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HIGHER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SUM</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K6" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B6)</s:f>
+        <s:v>3000000</s:v>
+      </s:c>
+      <s:c r="L6" s="4">
+        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B6)</s:f>
+        <s:v>2640000.0</s:v>
+      </s:c>
+      <s:c r="M6" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B6)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N6" s="4">
+        <s:f>IF(I6="HIGHER_IS_BETTER",MAX(0,K6-L6),MAX(0,L6-K6))</s:f>
+        <s:v>360000.0</s:v>
+      </s:c>
+      <s:c r="O6" s="5">
+        <s:f>IF(I6="HIGHER_IS_BETTER",IF(K6&gt;0,L6/K6,""),IF(L6&gt;0,K6/L6,""))</s:f>
+        <s:v>0.88</s:v>
+      </s:c>
+      <s:c r="P6" s="3" t="str">
+        <s:f>IF(IF(I6="HIGHER_IS_BETTER",L6&gt;=K6,L6&lt;=K6),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S6" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="7">
+      <s:c r="A7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-2-RESOLVED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-2-RESOLVED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-CS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESOLVED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>CASE</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HIGHER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SUM</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K7" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B7)</s:f>
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="L7" s="4">
+        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B7)</s:f>
+        <s:v>27</s:v>
+      </s:c>
+      <s:c r="M7" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B7)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N7" s="4">
+        <s:f>IF(I7="HIGHER_IS_BETTER",MAX(0,K7-L7),MAX(0,L7-K7))</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="O7" s="5">
+        <s:f>IF(I7="HIGHER_IS_BETTER",IF(K7&gt;0,L7/K7,""),IF(L7&gt;0,K7/L7,""))</s:f>
+        <s:v>0.9</s:v>
+      </s:c>
+      <s:c r="P7" s="3" t="str">
+        <s:f>IF(IF(I7="HIGHER_IS_BETTER",L7&gt;=K7,L7&lt;=K7),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S7" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="8">
+      <s:c r="A8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-2-RESPONSE_HOURS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-2-RESPONSE_HOURS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-CS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESPONSE_HOURS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HOUR</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>LOWER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>AVG</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K8" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B8)</s:f>
+        <s:v>24</s:v>
+      </s:c>
+      <s:c r="L8" s="4">
+        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B8)</s:f>
+        <s:v>24.0</s:v>
+      </s:c>
+      <s:c r="M8" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B8)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N8" s="4">
+        <s:f>IF(I8="HIGHER_IS_BETTER",MAX(0,K8-L8),MAX(0,L8-K8))</s:f>
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="O8" s="5">
+        <s:f>IF(I8="HIGHER_IS_BETTER",IF(K8&gt;0,L8/K8,""),IF(L8&gt;0,K8/L8,""))</s:f>
+        <s:v>1.0</s:v>
+      </s:c>
+      <s:c r="P8" s="3" t="str">
+        <s:f>IF(IF(I8="HIGHER_IS_BETTER",L8&gt;=K8,L8&lt;=K8),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>ON_TARGET</s:v>
+      </s:c>
+      <s:c r="Q8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S8" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="9">
+      <s:c r="A9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>RESULT-2-SATISFACTION</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>PLAN-2-SATISFACTION</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>GOAL-EXPERIENCE-2026</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>UNIT-CS</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SATISFACTION</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-01</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-02-28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>SCORE_1_5</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="I9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>HIGHER_IS_BETTER</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="J9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>AVG</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="K9" s="4">
+        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B9)</s:f>
+        <s:v>4.0</s:v>
+      </s:c>
+      <s:c r="L9" s="4">
+        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B9)</s:f>
+        <s:v>3.666667</s:v>
+      </s:c>
+      <s:c r="M9" s="2">
+        <s:f>COUNTIFS('KPI_Measurement'!B:B,B9)</s:f>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="N9" s="4">
+        <s:f>IF(I9="HIGHER_IS_BETTER",MAX(0,K9-L9),MAX(0,L9-K9))</s:f>
+        <s:v>0.333333</s:v>
+      </s:c>
+      <s:c r="O9" s="5">
+        <s:f>IF(I9="HIGHER_IS_BETTER",IF(K9&gt;0,L9/K9,""),IF(L9&gt;0,K9/L9,""))</s:f>
+        <s:v>0.916667</s:v>
+      </s:c>
+      <s:c r="P9" s="3" t="str">
+        <s:f>IF(IF(I9="HIGHER_IS_BETTER",L9&gt;=K9,L9&lt;=K9),"ON_TARGET","BELOW_TARGET")</s:f>
+        <s:v>BELOW_TARGET</s:v>
+      </s:c>
+      <s:c r="Q9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>FINAL_SIMULATED</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="R9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="S9" s="3" t="inlineStr">
+        <s:is>
+          <s:t>2026-03-03T09:00:00+07:00</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+  </s:sheetData>
+  <s:autoFilter ref="A1:S9"/>
+  <s:dataValidations count="2">
+    <s:dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <s:formula1>=REF_unit_code</s:formula1>
+    </s:dataValidation>
+    <s:dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
+      <s:formula1>=REF_indicator_code</s:formula1>
+    </s:dataValidation>
+  </s:dataValidations>
+  <s:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <s:tableParts count="1">
+    <s:tablePart r:id="rId1"/>
+  </s:tableParts>
+</s:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002563EB"/>
@@ -3634,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3686,73 +5902,81 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Master_Unit</t>
+          <t>Formula_Analitik</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>EXCLUDED</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>satu baris per unit</t>
+          <t>Satu baris per kode kontrol</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>unit_code</t>
+          <t>formula_code</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Registry master</t>
+          <t>API analytics-rules</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Review definisi sebelum menambahkan metrik</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Review terpisah sebelum evaluate</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Tidak di-load sebagai tabel bisnis; jangan ubah header.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Master_Tim</t>
+          <t>Aturan_Action_Plan</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>EXCLUDED</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>satu baris per tim penanggung jawab</t>
+          <t>Satu baris per kode kontrol</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>owner_team_code</t>
+          <t>rule_code</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Registry master</t>
+          <t>API analytics-rules</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Review definisi sebelum menambahkan metrik</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Review terpisah sebelum evaluate</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Tidak di-load sebagai tabel bisnis; jangan ubah header.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Master_Indikator</t>
+          <t>Master_Unit</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3762,12 +5986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>satu baris per indikator dengan definisi dan satuan</t>
+          <t>satu baris per unit</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>indicator_code</t>
+          <t>unit_code</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3785,27 +6009,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KPI_Plan</t>
+          <t>Master_Tim</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>NON_MASTER</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>satu baris per unit indikator periode versi target aktif</t>
+          <t>satu baris per tim penanggung jawab</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>owner_team_code</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>UPSERT</t>
+          <t>Registry master</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3813,53 +6037,45 @@
           <t>Review definisi sebelum menambahkan metrik</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>goal_id bukan business key karena satu goal dapat memiliki banyak indikator/periode. Versi target direview sebelum evaluasi.</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KPI_Measurement</t>
+          <t>Master_Indikator</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NON_MASTER</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>satu baris per bukti pengukuran indikator</t>
+          <t>satu baris per indikator dengan definisi dan satuan</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>measurement_id</t>
+          <t>indicator_code</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>UPSERT</t>
+          <t>Registry master</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>m_revenue_observed:sum [IDR] dengan filter indikator; m_resolved_observed:sum [CASE] dengan filter indikator; m_response_hours_observed:avg [HOUR] dengan filter indikator; m_satisfaction_observed:avg [SCORE_1_5] dengan filter indikator</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Nilai berbeda satuan tidak dijumlahkan. Rekap aktual mengikuti SUM/AVG pada Master_Indikator; 3 sampel tidak mewakili populasi tanpa bukti.</t>
-        </is>
-      </c>
+          <t>Review definisi sebelum menambahkan metrik</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KPI_Result</t>
+          <t>KPI_Plan</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3869,12 +6085,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>satu baris per plan indikator periode</t>
+          <t>satu baris per unit indikator periode versi target aktif</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>kpi_result_id</t>
+          <t>plan_id</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3884,59 +6100,314 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>m_revenue_target_value:max [IDR] dengan filter indikator; m_revenue_actual_value:max [IDR] dengan filter indikator; m_resolved_target_value:max [CASE] dengan filter indikator; m_resolved_actual_value:max [CASE] dengan filter indikator; m_response_hours_target_value:max [HOUR] dengan filter indikator; m_response_hours_actual_value:max [HOUR] dengan filter indikator; m_satisfaction_target_value:max [SCORE_1_5] dengan filter indikator; m_satisfaction_actual_value:max [SCORE_1_5] dengan filter indikator</t>
+          <t>Review definisi sebelum menambahkan metrik</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Jangan SUM actual/gap/achievement lintas indikator atau AVG rasio tanpa bobot yang sah. Actual rekap perlu dihitung ulang jika pengukuran berubah; rasio arah LOWER berbeda dari HIGHER.</t>
+          <t>goal_id bukan business key karena satu goal dapat memiliki banyak indikator/periode. Versi target direview sebelum evaluasi.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>KPI_Measurement</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NON_MASTER</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>satu baris per bukti pengukuran indikator</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>measurement_id</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UPSERT</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>m_revenue_observed:sum [IDR] dengan filter indikator; m_resolved_observed:sum [CASE] dengan filter indikator; m_response_hours_observed:avg [HOUR] dengan filter indikator; m_satisfaction_observed:avg [SCORE_1_5] dengan filter indikator</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Nilai berbeda satuan tidak dijumlahkan. Rekap aktual mengikuti SUM/AVG pada Master_Indikator; 3 sampel tidak mewakili populasi tanpa bukti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>KPI_Result</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NON_MASTER</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>satu baris per plan indikator periode</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>kpi_result_id</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>UPSERT</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>m_revenue_target_value:max [IDR] dengan filter indikator; m_revenue_actual_value:max [IDR] dengan filter indikator; m_resolved_target_value:max [CASE] dengan filter indikator; m_resolved_actual_value:max [CASE] dengan filter indikator; m_response_hours_target_value:max [HOUR] dengan filter indikator; m_response_hours_actual_value:max [HOUR] dengan filter indikator; m_satisfaction_target_value:max [SCORE_1_5] dengan filter indikator; m_satisfaction_actual_value:max [SCORE_1_5] dengan filter indikator</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Jangan SUM actual/gap/achievement lintas indikator atau AVG rasio tanpa bobot yang sah. Actual rekap perlu dihitung ulang jika pengukuran berubah; rasio arah LOWER berbeda dari HIGHER.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Action_Plan</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NON_MASTER</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>satu baris per tindakan yang merujuk record temuan</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>action_id</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>UPSERT</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Review definisi sebelum menambahkan metrik</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Baseline dibekukan sesuai periode bukti; hipotesis belum terverifikasi. Nilai follow-up kosong berarti belum dievaluasi, bukan nol.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D97706"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>formula_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>expression</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>output_unit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>revenue_achievement</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>m_revenue_actual_value / m_revenue_target_value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Ambang dan formula contoh; verifikasi unit, metode, grain dan target dengan pemilik bisnis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D97706"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rule_code</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>formula_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>operator</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>threshold_upper</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>action_description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>owner_team_code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>due_days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>review_revenue_achievement</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>revenue_achievement</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>gt</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Capaian pendapatan di atas 50%: review pipeline untuk mengejar target penuh; bukan berarti target tercapai.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>TEAM-MKT</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4027,7 +6498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4127,7 +6598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00047857"/>
@@ -4447,7 +6918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002563EB"/>
@@ -5074,2168 +7545,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002563EB"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>measurement_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>plan_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>unit_code</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>indicator_code</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>measured_at</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>measured_value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>measurement_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>evidence_ref</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>method_version</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>collected_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-0-0</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-REVENUE</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-MKT</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>700000</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-0-0</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-0-1</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-REVENUE</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-MKT</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-0-1</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-REVENUE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-MKT</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-0-2</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-1-0</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-RESOLVED</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-1-0</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-1-1</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-RESOLVED</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-1-1</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-1-2</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-RESOLVED</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-1-2</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-2-0</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-2-0</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-2-1</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-2-1</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-2-2</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-2-2</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-3-0</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-SATISFACTION</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-3-0</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-3-1</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-SATISFACTION</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-3-1</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-1-3-2</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-1-SATISFACTION</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-1-3-2</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-0-0</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-REVENUE</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-MKT</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>770000</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-0-0</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-0-1</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-REVENUE</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-MKT</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>880000</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-0-1</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-0-2</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-REVENUE</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-MKT</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>990000</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-0-2</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-1-0</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-RESOLVED</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-1-0</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-1-1</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-RESOLVED</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-1-1</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-1-2</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-RESOLVED</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>CASE</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-1-2</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-2-0</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-2-0</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-2-1</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-2-1</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-2-2</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSE_HOURS</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>HOUR</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-2-2</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-3-0</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-SATISFACTION</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-12T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-3-0</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-3-1</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-SATISFACTION</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-13T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-3-1</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>MEAS-2-3-2</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>PLAN-2-SATISFACTION</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>UNIT-CS</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>SATISFACTION</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-14T09:00:00+07:00</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>SCORE_1_5</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>SIMULASI-MEAS-2-3-2</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>METHOD-V1</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-03T09:00:00+07:00</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J25"/>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <formula1>=REF_unit_code</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <formula1>=REF_indicator_code</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:sheetPr>
-    <s:tabColor rgb="002563EB"/>
-    <s:outlinePr summaryBelow="1" summaryRight="1"/>
-    <s:pageSetUpPr/>
-  </s:sheetPr>
-  <s:dimension ref="A1:S9"/>
-  <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <s:cols>
-    <s:col width="18" customWidth="1" min="1" max="1"/>
-    <s:col width="18" customWidth="1" min="2" max="2"/>
-    <s:col width="18" customWidth="1" min="3" max="3"/>
-    <s:col width="18" customWidth="1" min="4" max="4"/>
-    <s:col width="18" customWidth="1" min="5" max="5"/>
-    <s:col width="18" customWidth="1" min="6" max="6"/>
-    <s:col width="18" customWidth="1" min="7" max="7"/>
-    <s:col width="19" customWidth="1" min="8" max="8"/>
-    <s:col width="18" customWidth="1" min="9" max="9"/>
-    <s:col width="18" customWidth="1" min="10" max="10"/>
-    <s:col width="18" customWidth="1" min="11" max="11"/>
-    <s:col width="18" customWidth="1" min="12" max="12"/>
-    <s:col width="18" customWidth="1" min="13" max="13"/>
-    <s:col width="19" customWidth="1" min="14" max="14"/>
-    <s:col width="20" customWidth="1" min="15" max="15"/>
-    <s:col width="18" customWidth="1" min="16" max="16"/>
-    <s:col width="19" customWidth="1" min="17" max="17"/>
-    <s:col width="18" customWidth="1" min="18" max="18"/>
-    <s:col width="18" customWidth="1" min="19" max="19"/>
-  </s:cols>
-  <s:sheetData>
-    <s:row r="1" ht="32" customHeight="1">
-      <s:c r="A1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>kpi_result_id</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>plan_id</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>goal_id</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>unit_code</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>indicator_code</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>period_start</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>period_end</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>measurement_unit</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>direction</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>aggregation</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>target_value</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="L1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>actual_value</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="M1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>sample_count</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="N1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>unfavourable_gap</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="O1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>achievement_ratio</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="P1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>result_status</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="Q1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>reporting_status</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>collected_at</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>data_as_of_at</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="2">
-      <s:c r="A2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-1-REVENUE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-1-REVENUE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-MKT</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>REVENUE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>IDR</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HIGHER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SUM</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K2" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B2)</s:f>
-        <s:v>3000000</s:v>
-      </s:c>
-      <s:c r="L2" s="4">
-        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B2)</s:f>
-        <s:v>2400000</s:v>
-      </s:c>
-      <s:c r="M2" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B2)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N2" s="4">
-        <s:f>IF(I2="HIGHER_IS_BETTER",MAX(0,K2-L2),MAX(0,L2-K2))</s:f>
-        <s:v>600000</s:v>
-      </s:c>
-      <s:c r="O2" s="5">
-        <s:f>IF(I2="HIGHER_IS_BETTER",IF(K2&gt;0,L2/K2,""),IF(L2&gt;0,K2/L2,""))</s:f>
-        <s:v>0.8</s:v>
-      </s:c>
-      <s:c r="P2" s="3" t="str">
-        <s:f>IF(IF(I2="HIGHER_IS_BETTER",L2&gt;=K2,L2&lt;=K2),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S2" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="3">
-      <s:c r="A3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-1-RESOLVED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-1-RESOLVED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-CS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESOLVED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>CASE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HIGHER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SUM</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K3" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B3)</s:f>
-        <s:v>30</s:v>
-      </s:c>
-      <s:c r="L3" s="4">
-        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B3)</s:f>
-        <s:v>24</s:v>
-      </s:c>
-      <s:c r="M3" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B3)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N3" s="4">
-        <s:f>IF(I3="HIGHER_IS_BETTER",MAX(0,K3-L3),MAX(0,L3-K3))</s:f>
-        <s:v>6</s:v>
-      </s:c>
-      <s:c r="O3" s="5">
-        <s:f>IF(I3="HIGHER_IS_BETTER",IF(K3&gt;0,L3/K3,""),IF(L3&gt;0,K3/L3,""))</s:f>
-        <s:v>0.8</s:v>
-      </s:c>
-      <s:c r="P3" s="3" t="str">
-        <s:f>IF(IF(I3="HIGHER_IS_BETTER",L3&gt;=K3,L3&lt;=K3),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S3" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="4">
-      <s:c r="A4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-1-RESPONSE_HOURS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-1-RESPONSE_HOURS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-CS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESPONSE_HOURS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HOUR</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>LOWER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>AVG</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K4" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B4)</s:f>
-        <s:v>24</s:v>
-      </s:c>
-      <s:c r="L4" s="4">
-        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B4)</s:f>
-        <s:v>30.0</s:v>
-      </s:c>
-      <s:c r="M4" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B4)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N4" s="4">
-        <s:f>IF(I4="HIGHER_IS_BETTER",MAX(0,K4-L4),MAX(0,L4-K4))</s:f>
-        <s:v>6.0</s:v>
-      </s:c>
-      <s:c r="O4" s="5">
-        <s:f>IF(I4="HIGHER_IS_BETTER",IF(K4&gt;0,L4/K4,""),IF(L4&gt;0,K4/L4,""))</s:f>
-        <s:v>0.8</s:v>
-      </s:c>
-      <s:c r="P4" s="3" t="str">
-        <s:f>IF(IF(I4="HIGHER_IS_BETTER",L4&gt;=K4,L4&lt;=K4),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S4" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="5">
-      <s:c r="A5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-1-SATISFACTION</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-1-SATISFACTION</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-CS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SATISFACTION</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-01-31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SCORE_1_5</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HIGHER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>AVG</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K5" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B5)</s:f>
-        <s:v>4.0</s:v>
-      </s:c>
-      <s:c r="L5" s="4">
-        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B5)</s:f>
-        <s:v>3.333333</s:v>
-      </s:c>
-      <s:c r="M5" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B5)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N5" s="4">
-        <s:f>IF(I5="HIGHER_IS_BETTER",MAX(0,K5-L5),MAX(0,L5-K5))</s:f>
-        <s:v>0.666667</s:v>
-      </s:c>
-      <s:c r="O5" s="5">
-        <s:f>IF(I5="HIGHER_IS_BETTER",IF(K5&gt;0,L5/K5,""),IF(L5&gt;0,K5/L5,""))</s:f>
-        <s:v>0.833333</s:v>
-      </s:c>
-      <s:c r="P5" s="3" t="str">
-        <s:f>IF(IF(I5="HIGHER_IS_BETTER",L5&gt;=K5,L5&lt;=K5),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S5" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="6">
-      <s:c r="A6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-2-REVENUE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-2-REVENUE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-MKT</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>REVENUE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>IDR</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HIGHER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SUM</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K6" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B6)</s:f>
-        <s:v>3000000</s:v>
-      </s:c>
-      <s:c r="L6" s="4">
-        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B6)</s:f>
-        <s:v>2640000.0</s:v>
-      </s:c>
-      <s:c r="M6" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B6)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N6" s="4">
-        <s:f>IF(I6="HIGHER_IS_BETTER",MAX(0,K6-L6),MAX(0,L6-K6))</s:f>
-        <s:v>360000.0</s:v>
-      </s:c>
-      <s:c r="O6" s="5">
-        <s:f>IF(I6="HIGHER_IS_BETTER",IF(K6&gt;0,L6/K6,""),IF(L6&gt;0,K6/L6,""))</s:f>
-        <s:v>0.88</s:v>
-      </s:c>
-      <s:c r="P6" s="3" t="str">
-        <s:f>IF(IF(I6="HIGHER_IS_BETTER",L6&gt;=K6,L6&lt;=K6),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S6" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="7">
-      <s:c r="A7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-2-RESOLVED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-2-RESOLVED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-CS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESOLVED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>CASE</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HIGHER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SUM</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K7" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B7)</s:f>
-        <s:v>30</s:v>
-      </s:c>
-      <s:c r="L7" s="4">
-        <s:f>SUMIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B7)</s:f>
-        <s:v>27</s:v>
-      </s:c>
-      <s:c r="M7" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B7)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N7" s="4">
-        <s:f>IF(I7="HIGHER_IS_BETTER",MAX(0,K7-L7),MAX(0,L7-K7))</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="O7" s="5">
-        <s:f>IF(I7="HIGHER_IS_BETTER",IF(K7&gt;0,L7/K7,""),IF(L7&gt;0,K7/L7,""))</s:f>
-        <s:v>0.9</s:v>
-      </s:c>
-      <s:c r="P7" s="3" t="str">
-        <s:f>IF(IF(I7="HIGHER_IS_BETTER",L7&gt;=K7,L7&lt;=K7),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S7" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="8">
-      <s:c r="A8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-2-RESPONSE_HOURS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-2-RESPONSE_HOURS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-CS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESPONSE_HOURS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HOUR</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>LOWER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>AVG</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K8" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B8)</s:f>
-        <s:v>24</s:v>
-      </s:c>
-      <s:c r="L8" s="4">
-        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B8)</s:f>
-        <s:v>24.0</s:v>
-      </s:c>
-      <s:c r="M8" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B8)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N8" s="4">
-        <s:f>IF(I8="HIGHER_IS_BETTER",MAX(0,K8-L8),MAX(0,L8-K8))</s:f>
-        <s:v>0</s:v>
-      </s:c>
-      <s:c r="O8" s="5">
-        <s:f>IF(I8="HIGHER_IS_BETTER",IF(K8&gt;0,L8/K8,""),IF(L8&gt;0,K8/L8,""))</s:f>
-        <s:v>1.0</s:v>
-      </s:c>
-      <s:c r="P8" s="3" t="str">
-        <s:f>IF(IF(I8="HIGHER_IS_BETTER",L8&gt;=K8,L8&lt;=K8),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>ON_TARGET</s:v>
-      </s:c>
-      <s:c r="Q8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S8" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="9">
-      <s:c r="A9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>RESULT-2-SATISFACTION</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>PLAN-2-SATISFACTION</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>GOAL-EXPERIENCE-2026</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>UNIT-CS</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SATISFACTION</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="F9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-01</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-02-28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>SCORE_1_5</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="I9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>HIGHER_IS_BETTER</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="J9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>AVG</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="K9" s="4">
-        <s:f>SUMIFS('KPI_Plan'!J:J,'KPI_Plan'!A:A,B9)</s:f>
-        <s:v>4.0</s:v>
-      </s:c>
-      <s:c r="L9" s="4">
-        <s:f>AVERAGEIFS('KPI_Measurement'!F:F,'KPI_Measurement'!B:B,B9)</s:f>
-        <s:v>3.666667</s:v>
-      </s:c>
-      <s:c r="M9" s="2">
-        <s:f>COUNTIFS('KPI_Measurement'!B:B,B9)</s:f>
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="N9" s="4">
-        <s:f>IF(I9="HIGHER_IS_BETTER",MAX(0,K9-L9),MAX(0,L9-K9))</s:f>
-        <s:v>0.333333</s:v>
-      </s:c>
-      <s:c r="O9" s="5">
-        <s:f>IF(I9="HIGHER_IS_BETTER",IF(K9&gt;0,L9/K9,""),IF(L9&gt;0,K9/L9,""))</s:f>
-        <s:v>0.916667</s:v>
-      </s:c>
-      <s:c r="P9" s="3" t="str">
-        <s:f>IF(IF(I9="HIGHER_IS_BETTER",L9&gt;=K9,L9&lt;=K9),"ON_TARGET","BELOW_TARGET")</s:f>
-        <s:v>BELOW_TARGET</s:v>
-      </s:c>
-      <s:c r="Q9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>FINAL_SIMULATED</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="R9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="S9" s="3" t="inlineStr">
-        <s:is>
-          <s:t>2026-03-03T09:00:00+07:00</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-  </s:sheetData>
-  <s:autoFilter ref="A1:S9"/>
-  <s:dataValidations count="2">
-    <s:dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <s:formula1>=REF_unit_code</s:formula1>
-    </s:dataValidation>
-    <s:dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Kode belum ada di master" error="Pilih kode rujukan yang sah; master baru harus direview sebelum dipakai." type="list">
-      <s:formula1>=REF_indicator_code</s:formula1>
-    </s:dataValidation>
-  </s:dataValidations>
-  <s:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <s:tableParts count="1">
-    <s:tablePart r:id="rId1"/>
-  </s:tableParts>
-</s:worksheet>
 </file>